--- a/data/baidu/china_biography.xlsx
+++ b/data/baidu/china_biography.xlsx
@@ -583,16 +583,24 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>末代皇帝</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>末代皇帝</t>
+        </is>
+      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -660,16 +668,24 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>南海十三郎</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>南海十三郎</t>
+        </is>
+      </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
@@ -734,24 +750,30 @@
           <t>https://movie.douban.com/subject/27060077/</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>49619.57142857143</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>绿皮书</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>绿皮书</t>
+        </is>
+      </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -814,16 +836,24 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>剃头匠</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>剃头匠</t>
+        </is>
+      </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
@@ -976,16 +1006,24 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>童年往事</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>童年往事</t>
+        </is>
+      </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
@@ -1053,16 +1091,24 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>阮玲玉</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>阮玲玉</t>
+        </is>
+      </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
@@ -1130,16 +1176,24 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
       <c r="T9" t="n">
         <v>0</v>
       </c>
@@ -1207,16 +1261,24 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>我的1919</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>我的1919</t>
+        </is>
+      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
@@ -1284,16 +1346,24 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>袁隆平</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>袁隆平</t>
+        </is>
+      </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
@@ -1361,16 +1431,24 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>周恩来</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>周恩来</t>
+        </is>
+      </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
@@ -1438,16 +1516,24 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>跛豪</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>跛豪</t>
+        </is>
+      </c>
       <c r="T13" t="n">
         <v>0</v>
       </c>
@@ -1512,24 +1598,30 @@
           <t>https://movie.douban.com/subject/3821067/</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>27751.85714285714</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>一代宗师</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>一代宗师</t>
+        </is>
+      </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1592,16 +1684,24 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>集结号</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>集结号</t>
+        </is>
+      </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
@@ -1669,16 +1769,24 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>戏梦人生</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>戏梦人生</t>
+        </is>
+      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -1746,16 +1854,24 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>巴尔扎克与小裁缝</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>巴尔扎克与小裁缝</t>
+        </is>
+      </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
@@ -1823,16 +1939,24 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>叶问</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>叶问</t>
+        </is>
+      </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
@@ -1897,21 +2021,27 @@
           <t>https://movie.douban.com/subject/35358429/</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>特级英雄黄继光</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>特级英雄黄继光</t>
+        </is>
+      </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1977,16 +2107,24 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>达摩祖师</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>达摩祖师</t>
+        </is>
+      </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
@@ -2139,16 +2277,24 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>拉贝日记</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>拉贝日记</t>
+        </is>
+      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -2216,16 +2362,24 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>一轮明月</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>一轮明月</t>
+        </is>
+      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
@@ -2293,16 +2447,24 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>叶问2：宗师传奇</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>叶问2</t>
+        </is>
+      </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
@@ -2370,16 +2532,24 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2653699803, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>教授与疯子</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>教授与疯子</t>
+        </is>
+      </c>
       <c r="T25" t="n">
         <v>0</v>
       </c>
@@ -2444,24 +2614,30 @@
           <t>https://movie.douban.com/subject/10545939/</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr"/>
+      <c r="O26" t="n">
+        <v>18019.14285714286</v>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>黄金时代</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>黄金时代</t>
+        </is>
+      </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -2524,16 +2700,24 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>中国最后一个太监</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>中国最后一个太监</t>
+        </is>
+      </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
@@ -2598,24 +2782,30 @@
           <t>https://movie.douban.com/subject/6041200/</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="n">
+        <v>5270.142857142857</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>钱学森</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>钱学森</t>
+        </is>
+      </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -2678,16 +2868,24 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>画魂</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>画魂</t>
+        </is>
+      </c>
       <c r="T29" t="n">
         <v>0</v>
       </c>
@@ -2755,16 +2953,24 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>霍元甲</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>霍元甲</t>
+        </is>
+      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -2829,24 +3035,30 @@
           <t>https://movie.douban.com/subject/6078003/</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr"/>
+      <c r="O31" t="n">
+        <v>3653.142857142857</v>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>柳如是</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>柳如是</t>
+        </is>
+      </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
@@ -2909,16 +3121,24 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>川岛芳子</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>川岛芳子</t>
+        </is>
+      </c>
       <c r="T32" t="n">
         <v>0</v>
       </c>
@@ -3069,16 +3289,24 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>七小福</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>七小福</t>
+        </is>
+      </c>
       <c r="T34" t="n">
         <v>0</v>
       </c>
@@ -3228,24 +3456,30 @@
           <t>https://movie.douban.com/subject/26440017/</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="n">
+        <v>2074.857142857143</v>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>启功</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>启功</t>
+        </is>
+      </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -3308,16 +3542,24 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>离开雷锋的日子</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>离开雷锋的日子</t>
+        </is>
+      </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
@@ -3385,16 +3627,24 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>武训传</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>武训传</t>
+        </is>
+      </c>
       <c r="T38" t="n">
         <v>0</v>
       </c>
@@ -3462,16 +3712,24 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>大太监李莲英</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>大太监李莲英</t>
+        </is>
+      </c>
       <c r="T39" t="n">
         <v>0</v>
       </c>
@@ -3621,24 +3879,30 @@
           <t>https://movie.douban.com/subject/26995719/</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr"/>
+      <c r="O41" t="n">
+        <v>2034.285714285714</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>金钱世界</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>金钱世界</t>
+        </is>
+      </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -3701,16 +3965,24 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>梅兰芳</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>梅兰芳</t>
+        </is>
+      </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
@@ -3775,24 +4047,30 @@
           <t>https://movie.douban.com/subject/6519575/</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr"/>
+      <c r="O43" t="n">
+        <v>2568.142857142857</v>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>杨善洲</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>杨善洲</t>
+        </is>
+      </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44">
@@ -3937,24 +4215,30 @@
           <t>https://movie.douban.com/subject/35132974/</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr"/>
+      <c r="O45" t="n">
+        <v>1165.428571428571</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>我的父亲焦裕禄</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>我的父亲焦裕禄</t>
+        </is>
+      </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46">
@@ -4014,24 +4298,30 @@
           <t>https://movie.douban.com/subject/30176790/</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="n">
+        <v>28709.42857142857</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>梅艳芳</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>梅艳芳</t>
+        </is>
+      </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47">
@@ -4091,24 +4381,30 @@
           <t>https://movie.douban.com/subject/11598977/</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr"/>
+      <c r="O47" t="n">
+        <v>40462.28571428572</v>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>叶问3</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>叶问3</t>
+        </is>
+      </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48">
@@ -4171,16 +4467,24 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2659250175, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>他们在岛屿写作：读中文系的人</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>他们在岛屿写作</t>
+        </is>
+      </c>
       <c r="T48" t="n">
         <v>0</v>
       </c>
@@ -4248,16 +4552,24 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>吴清源</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>吴清源</t>
+        </is>
+      </c>
       <c r="T49" t="n">
         <v>0</v>
       </c>
@@ -4322,24 +4634,30 @@
           <t>https://movie.douban.com/subject/32568661/</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr"/>
+      <c r="O50" t="n">
+        <v>3787.142857142857</v>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>妈妈的神奇小子</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>妈妈的神奇小子</t>
+        </is>
+      </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -4399,24 +4717,30 @@
           <t>https://movie.douban.com/subject/30295905/</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr"/>
+      <c r="O51" t="n">
+        <v>71114.28571428571</v>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>中国机长</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>中国机长</t>
+        </is>
+      </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
@@ -4476,21 +4800,27 @@
           <t>https://movie.douban.com/subject/32491917/</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr"/>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>我的喜马拉雅</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>我的喜马拉雅</t>
+        </is>
+      </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -4556,16 +4886,24 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2660923931, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>吾爱敦煌</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>吾爱敦煌</t>
+        </is>
+      </c>
       <c r="T53" t="n">
         <v>0</v>
       </c>
@@ -4718,16 +5056,24 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>火龙</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>火龙</t>
+        </is>
+      </c>
       <c r="T55" t="n">
         <v>0</v>
       </c>
@@ -4792,24 +5138,30 @@
           <t>https://movie.douban.com/subject/5343629/</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr"/>
+      <c r="O56" t="n">
+        <v>2252.285714285714</v>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>秋之白华</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>秋之白华</t>
+        </is>
+      </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57">
@@ -4869,24 +5221,30 @@
           <t>https://movie.douban.com/subject/6781971/</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr"/>
+      <c r="O57" t="n">
+        <v>4086.571428571428</v>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>萧红</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>萧红</t>
+        </is>
+      </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -4946,21 +5304,27 @@
           <t>https://movie.douban.com/subject/27073179/</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr"/>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>zero_valid</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>邻里美好的一天</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>邻里美好的一天</t>
+        </is>
+      </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -5026,16 +5390,24 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>怨女</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>怨女</t>
+        </is>
+      </c>
       <c r="T59" t="n">
         <v>0</v>
       </c>
@@ -5103,16 +5475,24 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2662733940, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>更好的我</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>更好的我</t>
+        </is>
+      </c>
       <c r="T60" t="n">
         <v>0</v>
       </c>
@@ -5177,24 +5557,30 @@
           <t>https://movie.douban.com/subject/10774103/</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr"/>
+      <c r="O61" t="n">
+        <v>408.1428571428572</v>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>画圣</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>画圣</t>
+        </is>
+      </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -5257,16 +5643,24 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2663695603, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>坐在人生的边上——杨绛</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>坐在人生的边上</t>
+        </is>
+      </c>
       <c r="T62" t="n">
         <v>0</v>
       </c>
@@ -5334,16 +5728,24 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>第一书记</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>第一书记</t>
+        </is>
+      </c>
       <c r="T63" t="n">
         <v>0</v>
       </c>
@@ -5577,16 +5979,24 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>鲁迅</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>鲁迅</t>
+        </is>
+      </c>
       <c r="T66" t="n">
         <v>0</v>
       </c>
@@ -5654,16 +6064,24 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>孔夫子</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>孔夫子</t>
+        </is>
+      </c>
       <c r="T67" t="n">
         <v>0</v>
       </c>
@@ -5731,16 +6149,24 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>雷锋</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>雷锋</t>
+        </is>
+      </c>
       <c r="T68" t="n">
         <v>0</v>
       </c>
@@ -5891,16 +6317,24 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>桂花巷</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>桂花巷</t>
+        </is>
+      </c>
       <c r="T70" t="n">
         <v>0</v>
       </c>
@@ -5968,16 +6402,24 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>我的法兰西岁月</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>我的法兰西岁月</t>
+        </is>
+      </c>
       <c r="T71" t="n">
         <v>0</v>
       </c>
@@ -6128,16 +6570,24 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2663932729, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>他们在岛屿写作：1918</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>他们在岛屿写作</t>
+        </is>
+      </c>
       <c r="T73" t="n">
         <v>0</v>
       </c>
@@ -6205,16 +6655,24 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>李小龙我的兄弟</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>李小龙我的兄弟</t>
+        </is>
+      </c>
       <c r="T74" t="n">
         <v>0</v>
       </c>
@@ -6282,16 +6740,24 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>小布什传</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>小布什传</t>
+        </is>
+      </c>
       <c r="T75" t="n">
         <v>0</v>
       </c>
@@ -6776,16 +7242,24 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>孔繁森</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>孔繁森</t>
+        </is>
+      </c>
       <c r="T81" t="n">
         <v>0</v>
       </c>
@@ -7021,16 +7495,24 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr"/>
-      <c r="S84" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>国歌</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>国歌</t>
+        </is>
+      </c>
       <c r="T84" t="n">
         <v>0</v>
       </c>
@@ -7268,16 +7750,24 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr"/>
-      <c r="S87" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>谭嗣同</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>谭嗣同</t>
+        </is>
+      </c>
       <c r="T87" t="n">
         <v>0</v>
       </c>
@@ -7345,16 +7835,24 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>郁达夫传奇</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>郁达夫传奇</t>
+        </is>
+      </c>
       <c r="T88" t="n">
         <v>0</v>
       </c>
@@ -7505,16 +8003,24 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>屈原</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>屈原</t>
+        </is>
+      </c>
       <c r="T90" t="n">
         <v>0</v>
       </c>
@@ -7582,16 +8088,24 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>告别紫禁城</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>告别紫禁城</t>
+        </is>
+      </c>
       <c r="T91" t="n">
         <v>0</v>
       </c>
@@ -7659,16 +8173,24 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr"/>
-      <c r="S92" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>马可波罗回香都</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>马可波罗回香都</t>
+        </is>
+      </c>
       <c r="T92" t="n">
         <v>0</v>
       </c>
@@ -7736,16 +8258,24 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2664098363, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>冯梦龙传奇</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>冯梦龙传奇</t>
+        </is>
+      </c>
       <c r="T93" t="n">
         <v>0</v>
       </c>
@@ -7813,16 +8343,24 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr"/>
-      <c r="S94" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>医痴叶天士</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>医痴叶天士</t>
+        </is>
+      </c>
       <c r="T94" t="n">
         <v>0</v>
       </c>
@@ -7890,16 +8428,24 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R95" t="inlineStr"/>
-      <c r="S95" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>孔子</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>孔子</t>
+        </is>
+      </c>
       <c r="T95" t="n">
         <v>0</v>
       </c>
@@ -8135,16 +8681,24 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>邓小平</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>邓小平</t>
+        </is>
+      </c>
       <c r="T98" t="n">
         <v>0</v>
       </c>
@@ -8465,16 +9019,24 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr"/>
-      <c r="S102" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2664900222, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>炼狱信使</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>炼狱信使</t>
+        </is>
+      </c>
       <c r="T102" t="n">
         <v>0</v>
       </c>
@@ -8712,16 +9274,24 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2665120736, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>奔跑的少年</t>
+        </is>
+      </c>
       <c r="T105" t="n">
         <v>0</v>
       </c>
@@ -8874,16 +9444,24 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>杨贵妃</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>杨贵妃</t>
+        </is>
+      </c>
       <c r="T107" t="n">
         <v>0</v>
       </c>
@@ -9206,16 +9784,24 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>董小宛</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>董小宛</t>
+        </is>
+      </c>
       <c r="T111" t="n">
         <v>0</v>
       </c>
@@ -9366,16 +9952,24 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2665274670, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>信仰者</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>信仰者</t>
+        </is>
+      </c>
       <c r="T113" t="n">
         <v>0</v>
       </c>
@@ -9945,16 +10539,24 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>任长霞</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>任长霞</t>
+        </is>
+      </c>
       <c r="T120" t="n">
         <v>0</v>
       </c>
@@ -10192,16 +10794,24 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R123" t="inlineStr"/>
-      <c r="S123" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>夜·明</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>夜·明</t>
+        </is>
+      </c>
       <c r="T123" t="n">
         <v>0</v>
       </c>
@@ -10439,16 +11049,24 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>顾城别恋</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>顾城别恋</t>
+        </is>
+      </c>
       <c r="T126" t="n">
         <v>0</v>
       </c>
@@ -10937,16 +11555,24 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr"/>
-      <c r="S132" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>白方礼</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>白方礼</t>
+        </is>
+      </c>
       <c r="T132" t="n">
         <v>0</v>
       </c>
@@ -11099,16 +11725,24 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>廖仲恺</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>廖仲恺</t>
+        </is>
+      </c>
       <c r="T134" t="n">
         <v>0</v>
       </c>
@@ -11176,16 +11810,24 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>白求恩：一个英雄的成长</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>白求恩</t>
+        </is>
+      </c>
       <c r="T135" t="n">
         <v>0</v>
       </c>
@@ -11253,16 +11895,24 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>冯志远</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>冯志远</t>
+        </is>
+      </c>
       <c r="T136" t="n">
         <v>0</v>
       </c>
@@ -11415,16 +12065,24 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>李小龙传奇</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>李小龙传奇</t>
+        </is>
+      </c>
       <c r="T138" t="n">
         <v>0</v>
       </c>
@@ -11660,16 +12318,24 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>定军山</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>定军山</t>
+        </is>
+      </c>
       <c r="T141" t="n">
         <v>0</v>
       </c>
@@ -11737,16 +12403,24 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>邓小平1928</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>邓小平1928</t>
+        </is>
+      </c>
       <c r="T142" t="n">
         <v>0</v>
       </c>
@@ -12065,16 +12739,24 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>詹天佑</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>詹天佑</t>
+        </is>
+      </c>
       <c r="T146" t="n">
         <v>0</v>
       </c>
@@ -12394,24 +13076,30 @@
           <t>https://movie.douban.com/subject/24860303/</t>
         </is>
       </c>
-      <c r="O150" t="inlineStr"/>
+      <c r="O150" t="n">
+        <v>447</v>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q150" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>门巴将军</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>门巴将军</t>
+        </is>
+      </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U150" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151">
@@ -12471,24 +13159,30 @@
           <t>https://movie.douban.com/subject/25700831/</t>
         </is>
       </c>
-      <c r="O151" t="inlineStr"/>
+      <c r="O151" t="n">
+        <v>1493.714285714286</v>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q151" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>大峰祖师</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>大峰祖师</t>
+        </is>
+      </c>
       <c r="T151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152">
@@ -12551,16 +13245,24 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2666842205, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>母亲的乒乓球</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>母亲的乒乓球</t>
+        </is>
+      </c>
       <c r="T152" t="n">
         <v>0</v>
       </c>
@@ -12710,24 +13412,30 @@
           <t>https://movie.douban.com/subject/22552302/</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="n">
+        <v>205.5714285714286</v>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q154" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>龙之诞生</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>龙之诞生</t>
+        </is>
+      </c>
       <c r="T154" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U154" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -12787,24 +13495,30 @@
           <t>https://movie.douban.com/subject/30185236/</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr"/>
+      <c r="O155" t="n">
+        <v>1542.142857142857</v>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q155" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>黄大年</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>黄大年</t>
+        </is>
+      </c>
       <c r="T155" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U155" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156">
@@ -12867,16 +13581,24 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>我的少女时代</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>我的少女时代</t>
+        </is>
+      </c>
       <c r="T156" t="n">
         <v>0</v>
       </c>
@@ -12944,16 +13666,24 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2667565559, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>“坏小子”乐团</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>“坏小子”乐团</t>
+        </is>
+      </c>
       <c r="T157" t="n">
         <v>0</v>
       </c>
@@ -13097,24 +13827,30 @@
           <t>https://movie.douban.com/subject/26691703/</t>
         </is>
       </c>
-      <c r="O159" t="inlineStr"/>
+      <c r="O159" t="n">
+        <v>665.2857142857143</v>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q159" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>股神</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>股神</t>
+        </is>
+      </c>
       <c r="T159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160">
@@ -13262,16 +13998,24 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>unsupported_date_range</t>
         </is>
       </c>
       <c r="Q161" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
+          <t>查询窗口早于百度指数最早支持日期 2011-01-01</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>李小龙与我</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>李小龙与我</t>
+        </is>
+      </c>
       <c r="T161" t="n">
         <v>0</v>
       </c>
@@ -13336,24 +14080,30 @@
           <t>https://movie.douban.com/subject/11627084/</t>
         </is>
       </c>
-      <c r="O162" t="inlineStr"/>
+      <c r="O162" t="n">
+        <v>927.8571428571429</v>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q162" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>吴仁宝</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>吴仁宝</t>
+        </is>
+      </c>
       <c r="T162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U162" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
@@ -13501,16 +14251,24 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q164" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2669118840, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>疯魔鲁智深</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>疯魔鲁智深</t>
+        </is>
+      </c>
       <c r="T164" t="n">
         <v>0</v>
       </c>
@@ -13578,16 +14336,24 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q165" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2669310098, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>宗师叶问</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>宗师叶问</t>
+        </is>
+      </c>
       <c r="T165" t="n">
         <v>0</v>
       </c>
@@ -13655,16 +14421,24 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q166" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2669461206, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>笑神穷不怕</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>笑神穷不怕</t>
+        </is>
+      </c>
       <c r="T166" t="n">
         <v>0</v>
       </c>
@@ -13732,16 +14506,24 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>missing_cache</t>
+          <t>bad_request</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="inlineStr"/>
+          <t>"ERROR-ErrorCode.UNKNOWN: 未知错误, {'status': 10002, 'data': '', 'logid': 2669622319, 'message': 'bad request'}"</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>毛泽东与齐白石</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>毛泽东与齐白石</t>
+        </is>
+      </c>
       <c r="T167" t="n">
         <v>0</v>
       </c>
@@ -13806,24 +14588,30 @@
           <t>https://movie.douban.com/subject/20438460/</t>
         </is>
       </c>
-      <c r="O168" t="inlineStr"/>
+      <c r="O168" t="n">
+        <v>302.2857142857143</v>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q168" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr"/>
-      <c r="S168" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>雷锋在1959</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>雷锋在1959</t>
+        </is>
+      </c>
       <c r="T168" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U168" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
@@ -13883,24 +14671,30 @@
           <t>https://movie.douban.com/subject/21363244/</t>
         </is>
       </c>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="n">
+        <v>387</v>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q169" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr"/>
-      <c r="S169" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>雷锋的微笑</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>雷锋的微笑</t>
+        </is>
+      </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U169" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
@@ -14045,24 +14839,30 @@
           <t>https://movie.douban.com/subject/11627079/</t>
         </is>
       </c>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="n">
+        <v>1073.428571428571</v>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q171" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr"/>
-      <c r="S171" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>青春雷锋</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>青春雷锋</t>
+        </is>
+      </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
@@ -14118,24 +14918,30 @@
           <t>https://movie.douban.com/subject/10757012/</t>
         </is>
       </c>
-      <c r="O172" t="inlineStr"/>
+      <c r="O172" t="n">
+        <v>1545.571428571429</v>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>missing_cache</t>
-        </is>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>未找到缓存文件</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr"/>
-      <c r="S172" t="inlineStr"/>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>戚继光英雄传</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>戚继光英雄传</t>
+        </is>
+      </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U172" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
